--- a/CRDO_Model.xlsx
+++ b/CRDO_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE760A2-BFDF-49F8-86BD-E71B4A07E740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED301F0-B0EA-495C-8137-DECC79A5C115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3192,10 +3192,10 @@
     <t>Intangibles</t>
   </si>
   <si>
-    <t>12/24/25</t>
-  </si>
-  <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -11074,10 +11074,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="44">
-        <v>150.37</v>
+        <v>146.18</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="4" spans="2:20">
@@ -11088,7 +11088,7 @@
         <v>175.30699999999999</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5" spans="2:20">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="C5" s="46">
         <f>C3*C4</f>
-        <v>26360.91359</v>
+        <v>25626.377260000001</v>
       </c>
     </row>
     <row r="6" spans="2:20">
@@ -11109,7 +11109,7 @@
         <v>813.57500000000005</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7" spans="2:20">
@@ -11120,7 +11120,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8" spans="2:20">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="C8" s="47">
         <f>C5-C6+C7</f>
-        <v>25547.338589999999</v>
+        <v>24812.80226</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15">
@@ -11403,9 +11403,6 @@
     <hyperlink ref="S13" r:id="rId3" xr:uid="{877B87AF-6848-4F1F-88DA-774FC3ABA11F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
@@ -16445,7 +16442,7 @@
       </c>
       <c r="AN65" s="59">
         <f>Main!C3</f>
-        <v>150.37</v>
+        <v>146.18</v>
       </c>
       <c r="AO65" s="60"/>
     </row>
@@ -16494,7 +16491,7 @@
       </c>
       <c r="AN66" s="53">
         <f>AN64/AN65-1</f>
-        <v>0.25115378185370774</v>
+        <v>0.28701596782967598</v>
       </c>
       <c r="AO66" s="61" t="str">
         <f>IF(AN66&gt;0,"Upside","Downside")</f>

--- a/CRDO_Model.xlsx
+++ b/CRDO_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED301F0-B0EA-495C-8137-DECC79A5C115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585ADF0A-7F98-40FC-B249-DABDA4900E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33390" yWindow="1470" windowWidth="21600" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -14248,43 +14248,43 @@
       </c>
       <c r="AE39" s="74">
         <f>SUM(AD53:AD54)*AN55</f>
-        <v>186.55022499999998</v>
+        <v>191.94184999999999</v>
       </c>
       <c r="AF39" s="74">
         <f>SUM(AE53:AE54)*$AN$55</f>
-        <v>316.57386028267126</v>
+        <v>328.07468147935248</v>
       </c>
       <c r="AG39" s="74">
         <f t="shared" ref="AG39:AN39" si="32">SUM(AF53:AF54)*$AN$55</f>
-        <v>660.72769271860579</v>
+        <v>687.17786993153015</v>
       </c>
       <c r="AH39" s="74">
         <f t="shared" si="32"/>
-        <v>1229.8001298653639</v>
+        <v>1284.1735579809031</v>
       </c>
       <c r="AI39" s="74">
         <f t="shared" si="32"/>
-        <v>2124.3908851051219</v>
+        <v>2227.9688467290539</v>
       </c>
       <c r="AJ39" s="74">
         <f t="shared" si="32"/>
-        <v>3483.6991810350141</v>
+        <v>3670.8120147990799</v>
       </c>
       <c r="AK39" s="74">
         <f t="shared" si="32"/>
-        <v>5487.740276378524</v>
+        <v>5811.8753234875485</v>
       </c>
       <c r="AL39" s="74">
         <f t="shared" si="32"/>
-        <v>8488.8134050781518</v>
+        <v>9036.7127609449926</v>
       </c>
       <c r="AM39" s="74">
         <f t="shared" si="32"/>
-        <v>12839.826706075155</v>
+        <v>13745.102344143286</v>
       </c>
       <c r="AN39" s="74">
         <f t="shared" si="32"/>
-        <v>19087.516252718015</v>
+        <v>20556.066228821153</v>
       </c>
     </row>
     <row r="40" spans="2:92">
@@ -14381,43 +14381,43 @@
       </c>
       <c r="AE40" s="74">
         <f>AE38+AE39</f>
-        <v>505.75783952500001</v>
+        <v>511.14946452499998</v>
       </c>
       <c r="AF40" s="74">
         <f t="shared" ref="AF40:AN40" si="34">AF38+AF39</f>
-        <v>814.04747260987119</v>
+        <v>825.54829380655246</v>
       </c>
       <c r="AG40" s="74">
         <f t="shared" si="34"/>
-        <v>1349.5122268190498</v>
+        <v>1375.9624040319741</v>
       </c>
       <c r="AH40" s="74">
         <f t="shared" si="34"/>
-        <v>2143.438270663411</v>
+        <v>2197.8116987789504</v>
       </c>
       <c r="AI40" s="74">
         <f t="shared" si="34"/>
-        <v>3273.8639111991633</v>
+        <v>3377.4418728230958</v>
       </c>
       <c r="AJ40" s="74">
         <f t="shared" si="34"/>
-        <v>4877.4958207326072</v>
+        <v>5064.6086544966729</v>
       </c>
       <c r="AK40" s="74">
         <f t="shared" si="34"/>
-        <v>7304.1025341031418</v>
+        <v>7628.2375812121663</v>
       </c>
       <c r="AL40" s="74">
         <f t="shared" si="34"/>
-        <v>10589.627748091276</v>
+        <v>11137.527103958117</v>
       </c>
       <c r="AM40" s="74">
         <f t="shared" si="34"/>
-        <v>15205.8157508801</v>
+        <v>16111.091388948231</v>
       </c>
       <c r="AN40" s="74">
         <f t="shared" si="34"/>
-        <v>21643.241098551553</v>
+        <v>23111.791074654691</v>
       </c>
     </row>
     <row r="41" spans="2:92">
@@ -14496,43 +14496,43 @@
       </c>
       <c r="AE41" s="74">
         <f>AE40*AE50</f>
-        <v>10.1151567905</v>
+        <v>10.222989290499999</v>
       </c>
       <c r="AF41" s="74">
         <f t="shared" ref="AF41:AN41" si="35">AF40*AF50</f>
-        <v>18.316068133722101</v>
+        <v>18.574836610647431</v>
       </c>
       <c r="AG41" s="74">
         <f t="shared" si="35"/>
-        <v>33.737805670476249</v>
+        <v>34.399060100799353</v>
       </c>
       <c r="AH41" s="74">
         <f t="shared" si="35"/>
-        <v>75.020339473219394</v>
+        <v>76.923409457263276</v>
       </c>
       <c r="AI41" s="74">
         <f t="shared" si="35"/>
-        <v>130.95455644796652</v>
+        <v>135.09767491292382</v>
       </c>
       <c r="AJ41" s="74">
         <f t="shared" si="35"/>
-        <v>243.87479103663037</v>
+        <v>253.23043272483366</v>
       </c>
       <c r="AK41" s="74">
         <f t="shared" si="35"/>
-        <v>365.20512670515711</v>
+        <v>381.41187906060833</v>
       </c>
       <c r="AL41" s="74">
         <f t="shared" si="35"/>
-        <v>529.48138740456386</v>
+        <v>556.87635519790581</v>
       </c>
       <c r="AM41" s="74">
         <f t="shared" si="35"/>
-        <v>760.29078754400507</v>
+        <v>805.55456944741161</v>
       </c>
       <c r="AN41" s="74">
         <f t="shared" si="35"/>
-        <v>1082.1620549275776</v>
+        <v>1155.5895537327347</v>
       </c>
     </row>
     <row r="42" spans="2:92" s="2" customFormat="1" ht="15">
@@ -14631,243 +14631,243 @@
       </c>
       <c r="AE42" s="76">
         <f>AE40-AE41</f>
-        <v>495.6426827345</v>
+        <v>500.9264752345</v>
       </c>
       <c r="AF42" s="76">
         <f t="shared" ref="AF42:AN42" si="37">AF40-AF41</f>
-        <v>795.73140447614912</v>
+        <v>806.97345719590498</v>
       </c>
       <c r="AG42" s="76">
         <f t="shared" si="37"/>
-        <v>1315.7744211485735</v>
+        <v>1341.5633439311748</v>
       </c>
       <c r="AH42" s="76">
         <f t="shared" si="37"/>
-        <v>2068.4179311901917</v>
+        <v>2120.8882893216869</v>
       </c>
       <c r="AI42" s="76">
         <f t="shared" si="37"/>
-        <v>3142.9093547511966</v>
+        <v>3242.3441979101717</v>
       </c>
       <c r="AJ42" s="76">
         <f t="shared" si="37"/>
-        <v>4633.6210296959771</v>
+        <v>4811.378221771839</v>
       </c>
       <c r="AK42" s="76">
         <f t="shared" si="37"/>
-        <v>6938.8974073979844</v>
+        <v>7246.8257021515583</v>
       </c>
       <c r="AL42" s="76">
         <f t="shared" si="37"/>
-        <v>10060.146360686713</v>
+        <v>10580.65074876021</v>
       </c>
       <c r="AM42" s="76">
         <f t="shared" si="37"/>
-        <v>14445.524963336095</v>
+        <v>15305.53681950082</v>
       </c>
       <c r="AN42" s="76">
         <f t="shared" si="37"/>
-        <v>20561.079043623977</v>
+        <v>21956.201520921957</v>
       </c>
       <c r="AO42" s="76">
         <f>AN42*(1+$AN$56)</f>
-        <v>20920.897926887399</v>
+        <v>22340.435047538092</v>
       </c>
       <c r="AP42" s="76">
         <f t="shared" ref="AP42:CL42" si="38">AO42*(1+$AN$56)</f>
-        <v>21287.013640607929</v>
+        <v>22731.392660870009</v>
       </c>
       <c r="AQ42" s="76">
         <f t="shared" si="38"/>
-        <v>21659.536379318568</v>
+        <v>23129.192032435236</v>
       </c>
       <c r="AR42" s="76">
         <f t="shared" si="38"/>
-        <v>22038.578265956643</v>
+        <v>23533.952893002854</v>
       </c>
       <c r="AS42" s="76">
         <f t="shared" si="38"/>
-        <v>22424.253385610886</v>
+        <v>23945.797068630407</v>
       </c>
       <c r="AT42" s="76">
         <f t="shared" si="38"/>
-        <v>22816.677819859076</v>
+        <v>24364.84851733144</v>
       </c>
       <c r="AU42" s="76">
         <f t="shared" si="38"/>
-        <v>23215.969681706611</v>
+        <v>24791.233366384742</v>
       </c>
       <c r="AV42" s="76">
         <f t="shared" si="38"/>
-        <v>23622.249151136479</v>
+        <v>25225.079950296476</v>
       </c>
       <c r="AW42" s="76">
         <f t="shared" si="38"/>
-        <v>24035.63851128137</v>
+        <v>25666.518849426666</v>
       </c>
       <c r="AX42" s="76">
         <f t="shared" si="38"/>
-        <v>24456.262185228796</v>
+        <v>26115.682929291634</v>
       </c>
       <c r="AY42" s="76">
         <f t="shared" si="38"/>
-        <v>24884.246773470302</v>
+        <v>26572.707380554239</v>
       </c>
       <c r="AZ42" s="76">
         <f t="shared" si="38"/>
-        <v>25319.721092006035</v>
+        <v>27037.72975971394</v>
       </c>
       <c r="BA42" s="76">
         <f t="shared" si="38"/>
-        <v>25762.816211116144</v>
+        <v>27510.890030508937</v>
       </c>
       <c r="BB42" s="76">
         <f t="shared" si="38"/>
-        <v>26213.665494810677</v>
+        <v>27992.330606042844</v>
       </c>
       <c r="BC42" s="76">
         <f t="shared" si="38"/>
-        <v>26672.404640969864</v>
+        <v>28482.196391648595</v>
       </c>
       <c r="BD42" s="76">
         <f t="shared" si="38"/>
-        <v>27139.171722186838</v>
+        <v>28980.634828502447</v>
       </c>
       <c r="BE42" s="76">
         <f t="shared" si="38"/>
-        <v>27614.107227325108</v>
+        <v>29487.795938001243</v>
       </c>
       <c r="BF42" s="76">
         <f t="shared" si="38"/>
-        <v>28097.3541038033</v>
+        <v>30003.832366916267</v>
       </c>
       <c r="BG42" s="76">
         <f t="shared" si="38"/>
-        <v>28589.057800619859</v>
+        <v>30528.899433337305</v>
       </c>
       <c r="BH42" s="76">
         <f t="shared" si="38"/>
-        <v>29089.366312130707</v>
+        <v>31063.15517342071</v>
       </c>
       <c r="BI42" s="76">
         <f t="shared" si="38"/>
-        <v>29598.430222592997</v>
+        <v>31606.760388955576</v>
       </c>
       <c r="BJ42" s="76">
         <f t="shared" si="38"/>
-        <v>30116.402751488375</v>
+        <v>32159.878695762302</v>
       </c>
       <c r="BK42" s="76">
         <f t="shared" si="38"/>
-        <v>30643.439799639422</v>
+        <v>32722.676572938144</v>
       </c>
       <c r="BL42" s="76">
         <f t="shared" si="38"/>
-        <v>31179.699996133113</v>
+        <v>33295.323412964564</v>
       </c>
       <c r="BM42" s="76">
         <f t="shared" si="38"/>
-        <v>31725.344746065446</v>
+        <v>33877.991572691448</v>
       </c>
       <c r="BN42" s="76">
         <f t="shared" si="38"/>
-        <v>32280.538279121592</v>
+        <v>34470.856425213547</v>
       </c>
       <c r="BO42" s="76">
         <f t="shared" si="38"/>
-        <v>32845.447699006225</v>
+        <v>35074.096412654784</v>
       </c>
       <c r="BP42" s="76">
         <f t="shared" si="38"/>
-        <v>33420.243033738836</v>
+        <v>35687.893099876244</v>
       </c>
       <c r="BQ42" s="76">
         <f t="shared" si="38"/>
-        <v>34005.097286829267</v>
+        <v>36312.431229124079</v>
       </c>
       <c r="BR42" s="76">
         <f t="shared" si="38"/>
-        <v>34600.18648934878</v>
+        <v>36947.898775633752</v>
       </c>
       <c r="BS42" s="76">
         <f t="shared" si="38"/>
-        <v>35205.689752912389</v>
+        <v>37594.487004207345</v>
       </c>
       <c r="BT42" s="76">
         <f t="shared" si="38"/>
-        <v>35821.78932358836</v>
+        <v>38252.390526780975</v>
       </c>
       <c r="BU42" s="76">
         <f t="shared" si="38"/>
-        <v>36448.670636751158</v>
+        <v>38921.807360999643</v>
       </c>
       <c r="BV42" s="76">
         <f t="shared" si="38"/>
-        <v>37086.522372894309</v>
+        <v>39602.938989817136</v>
       </c>
       <c r="BW42" s="76">
         <f t="shared" si="38"/>
-        <v>37735.53651441996</v>
+        <v>40295.990422138937</v>
       </c>
       <c r="BX42" s="76">
         <f t="shared" si="38"/>
-        <v>38395.908403422312</v>
+        <v>41001.170254526369</v>
       </c>
       <c r="BY42" s="76">
         <f t="shared" si="38"/>
-        <v>39067.836800482204</v>
+        <v>41718.690733980584</v>
       </c>
       <c r="BZ42" s="76">
         <f t="shared" si="38"/>
-        <v>39751.523944490647</v>
+        <v>42448.767821825248</v>
       </c>
       <c r="CA42" s="76">
         <f t="shared" si="38"/>
-        <v>40447.175613519234</v>
+        <v>43191.621258707193</v>
       </c>
       <c r="CB42" s="76">
         <f t="shared" si="38"/>
-        <v>41155.001186755821</v>
+        <v>43947.47463073457</v>
       </c>
       <c r="CC42" s="76">
         <f t="shared" si="38"/>
-        <v>41875.213707524053</v>
+        <v>44716.555436772425</v>
       </c>
       <c r="CD42" s="76">
         <f t="shared" si="38"/>
-        <v>42608.029947405725</v>
+        <v>45499.095156915944</v>
       </c>
       <c r="CE42" s="76">
         <f t="shared" si="38"/>
-        <v>43353.670471485326</v>
+        <v>46295.329322161975</v>
       </c>
       <c r="CF42" s="76">
         <f t="shared" si="38"/>
-        <v>44112.359704736322</v>
+        <v>47105.49758529981</v>
       </c>
       <c r="CG42" s="76">
         <f t="shared" si="38"/>
-        <v>44884.325999569213</v>
+        <v>47929.843793042557</v>
       </c>
       <c r="CH42" s="76">
         <f t="shared" si="38"/>
-        <v>45669.80170456168</v>
+        <v>48768.616059420805</v>
       </c>
       <c r="CI42" s="76">
         <f t="shared" si="38"/>
-        <v>46469.023234391512</v>
+        <v>49622.066840460669</v>
       </c>
       <c r="CJ42" s="76">
         <f t="shared" si="38"/>
-        <v>47282.231140993368</v>
+        <v>50490.453010168734</v>
       </c>
       <c r="CK42" s="76">
         <f t="shared" si="38"/>
-        <v>48109.670185960756</v>
+        <v>51374.035937846689</v>
       </c>
       <c r="CL42" s="76">
         <f t="shared" si="38"/>
-        <v>48951.589414215072</v>
+        <v>52273.081566759007</v>
       </c>
       <c r="CM42" s="34"/>
       <c r="CN42" s="34"/>
@@ -15768,43 +15768,43 @@
       </c>
       <c r="AE51" s="77">
         <f t="shared" si="54"/>
-        <v>0.43088209115403703</v>
+        <v>0.43547550419317105</v>
       </c>
       <c r="AF51" s="77">
         <f t="shared" si="54"/>
-        <v>0.47346530527135233</v>
+        <v>0.48015439896916856</v>
       </c>
       <c r="AG51" s="77">
         <f t="shared" si="54"/>
-        <v>0.59409848032030976</v>
+        <v>0.60574269500330002</v>
       </c>
       <c r="AH51" s="77">
         <f t="shared" si="54"/>
-        <v>0.73011923760775488</v>
+        <v>0.74864045486191466</v>
       </c>
       <c r="AI51" s="77">
         <f t="shared" si="54"/>
-        <v>0.89545625718476562</v>
+        <v>0.92378655323809822</v>
       </c>
       <c r="AJ51" s="77">
         <f t="shared" si="54"/>
-        <v>1.0920850753273319</v>
+        <v>1.1339801667156926</v>
       </c>
       <c r="AK51" s="77">
         <f t="shared" si="54"/>
-        <v>1.2797725902928068</v>
+        <v>1.3365652142882383</v>
       </c>
       <c r="AL51" s="77">
         <f t="shared" si="54"/>
-        <v>1.6281542317193305</v>
+        <v>1.7123937041570354</v>
       </c>
       <c r="AM51" s="77">
         <f t="shared" si="54"/>
-        <v>2.1063944160239405</v>
+        <v>2.2317982470468736</v>
       </c>
       <c r="AN51" s="77">
         <f t="shared" si="54"/>
-        <v>2.7755618065123633</v>
+        <v>2.9638908652733127</v>
       </c>
     </row>
     <row r="53" spans="2:41">
@@ -15842,43 +15842,43 @@
       </c>
       <c r="AE53" s="74">
         <f>AD53+AE42</f>
-        <v>731.96268273450005</v>
+        <v>737.24647523449994</v>
       </c>
       <c r="AF53" s="74">
         <f t="shared" ref="AF53:AN53" si="55">AE53+AF42</f>
-        <v>1527.6940872106493</v>
+        <v>1544.2199324304049</v>
       </c>
       <c r="AG53" s="74">
         <f t="shared" si="55"/>
-        <v>2843.4685083592231</v>
+        <v>2885.7832763615797</v>
       </c>
       <c r="AH53" s="74">
         <f t="shared" si="55"/>
-        <v>4911.8864395494147</v>
+        <v>5006.6715656832666</v>
       </c>
       <c r="AI53" s="74">
         <f t="shared" si="55"/>
-        <v>8054.7957943006113</v>
+        <v>8249.0157635934374</v>
       </c>
       <c r="AJ53" s="74">
         <f t="shared" si="55"/>
-        <v>12688.416823996587</v>
+        <v>13060.393985365277</v>
       </c>
       <c r="AK53" s="74">
         <f t="shared" si="55"/>
-        <v>19627.314231394572</v>
+        <v>20307.219687516837</v>
       </c>
       <c r="AL53" s="74">
         <f t="shared" si="55"/>
-        <v>29687.460592081283</v>
+        <v>30887.870436277048</v>
       </c>
       <c r="AM53" s="74">
         <f t="shared" si="55"/>
-        <v>44132.985555417377</v>
+        <v>46193.407255777871</v>
       </c>
       <c r="AN53" s="74">
         <f t="shared" si="55"/>
-        <v>64694.064599041354</v>
+        <v>68149.608776699824</v>
       </c>
     </row>
     <row r="54" spans="2:41">
@@ -15965,7 +15965,7 @@
         <v>124</v>
       </c>
       <c r="AN55" s="53">
-        <v>0.4325</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="AO55" s="50"/>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="AN62" s="55">
         <f>NPV(AN60,AE42:CL42)</f>
-        <v>32981.556731247299</v>
+        <v>34895.059636841572</v>
       </c>
       <c r="AO62" s="50"/>
     </row>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="AN64" s="59">
         <f>AN62/AN63</f>
-        <v>188.13599417734204</v>
+        <v>199.05114819625899</v>
       </c>
       <c r="AO64" s="49"/>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AN66" s="53">
         <f>AN64/AN65-1</f>
-        <v>0.28701596782967598</v>
+        <v>0.36168523872115865</v>
       </c>
       <c r="AO66" s="61" t="str">
         <f>IF(AN66&gt;0,"Upside","Downside")</f>
